--- a/assets/starter-pack/rebuilt/FLK_05_8a_Certification_Self_Assessment.xlsx
+++ b/assets/starter-pack/rebuilt/FLK_05_8a_Certification_Self_Assessment.xlsx
@@ -4,13 +4,15 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Inputs" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Calc" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Summary" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Instructions" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Program Reference" state="visible" r:id="rId8"/>
+    <sheet sheetId="1" name="Lists" state="veryHidden" r:id="rId4"/>
+    <sheet sheetId="2" name="Inputs" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Calc" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Summary" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Instructions" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Program Reference" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
+    <definedName name="YesNoMaybe">Lists!$A$2:$A$4</definedName>
     <definedName name="BusinessName">Inputs!$C$4</definedName>
     <definedName name="OwnerNames">Inputs!$C$5</definedName>
     <definedName name="PrimaryNAICS">Inputs!$C$6</definedName>
@@ -21,14 +23,26 @@
     <definedName name="TotalWeight">Calc!$E$29</definedName>
     <definedName name="TotalScore">Calc!$F$29</definedName>
     <definedName name="ReadinessPct">Calc!$G$29</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Inputs'!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Inputs'!$1:$10</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="114">
+  <si>
+    <t>Met? (Y / N / ?)</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
   <si>
     <t>8(a) BD PROGRAM — CERTIFICATION SELF-ASSESSMENT</t>
   </si>
@@ -421,12 +435,21 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -533,12 +556,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF047857"/>
+        <fgColor rgb="FFF1F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1F5F9"/>
+        <fgColor rgb="FF047857"/>
       </patternFill>
     </fill>
     <fill>
@@ -649,123 +672,129 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1237,6 +1266,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1251,588 +1314,588 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
     </row>
     <row r="4" ht="20" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="B4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" ht="20" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
+      <c r="B5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
     </row>
     <row r="6" ht="20" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="B6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
     </row>
     <row r="7" ht="20" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="B7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
     </row>
     <row r="8" ht="20" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
+      <c r="B8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
     </row>
     <row r="9" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
+        <v>1</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="13">
+        <v>2</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="9">
+        <v>3</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="13">
+        <v>4</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="9">
+        <v>5</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="13">
+        <v>6</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="9">
+        <v>7</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="13">
         <v>8</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B20" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="9">
         <v>9</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="B22" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="13">
         <v>10</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="B23" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="9">
         <v>11</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="B24" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="13">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="B26" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="9">
         <v>13</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>1</v>
-      </c>
-      <c r="B12" s="8" t="s">
+      <c r="B27" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="13">
         <v>14</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="10" t="s">
+      <c r="B28" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="9">
         <v>15</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
-        <v>2</v>
-      </c>
-      <c r="B13" s="12" t="s">
+      <c r="B29" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+    </row>
+    <row r="31" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="13">
         <v>16</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>3</v>
-      </c>
-      <c r="B14" s="8" t="s">
+      <c r="B31" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="9">
         <v>17</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="11">
-        <v>4</v>
-      </c>
-      <c r="B15" s="12" t="s">
+      <c r="B32" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="13">
         <v>18</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>5</v>
-      </c>
-      <c r="B16" s="8" t="s">
+      <c r="B33" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="E33" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="9">
+        <v>19</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+    </row>
+    <row r="36" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="13">
         <v>20</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="11">
-        <v>6</v>
-      </c>
-      <c r="B18" s="12" t="s">
+      <c r="B36" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="9">
         <v>21</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>7</v>
-      </c>
-      <c r="B19" s="8" t="s">
+      <c r="B37" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+    </row>
+    <row r="39" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="13">
         <v>22</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="11">
-        <v>8</v>
-      </c>
-      <c r="B20" s="12" t="s">
+      <c r="B39" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="9">
         <v>23</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="B40" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="13">
         <v>24</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
-        <v>9</v>
-      </c>
-      <c r="B22" s="8" t="s">
+      <c r="B41" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="9">
         <v>25</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="11">
-        <v>10</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
-        <v>11</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-    </row>
-    <row r="26" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="11">
-        <v>12</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
-        <v>13</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="11">
-        <v>14</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
-        <v>15</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-    </row>
-    <row r="31" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="11">
-        <v>16</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
-        <v>17</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="11">
-        <v>18</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
+      <c r="B42" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-    </row>
-    <row r="36" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="11">
-        <v>20</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="7">
-        <v>21</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-    </row>
-    <row r="39" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="11">
-        <v>22</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
-        <v>23</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="11">
-        <v>24</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="7">
-        <v>25</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>3</v>
+      <c r="E42" s="10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="44" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="45" ht="50" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
+      <c r="A45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1865,25 +1928,25 @@
   </conditionalFormatting>
   <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick one" error="Choose Y (yes / met), N (no / not met), or ? (unknown)." sqref="C12:C16">
-      <formula1>"Y,N,?"</formula1>
+      <formula1>YesNoMaybe</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick one" error="Choose Y (yes / met), N (no / not met), or ? (unknown)." sqref="C18:C20">
-      <formula1>"Y,N,?"</formula1>
+      <formula1>YesNoMaybe</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick one" error="Choose Y (yes / met), N (no / not met), or ? (unknown)." sqref="C22:C24">
-      <formula1>"Y,N,?"</formula1>
+      <formula1>YesNoMaybe</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick one" error="Choose Y (yes / met), N (no / not met), or ? (unknown)." sqref="C26:C29">
-      <formula1>"Y,N,?"</formula1>
+      <formula1>YesNoMaybe</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick one" error="Choose Y (yes / met), N (no / not met), or ? (unknown)." sqref="C31:C34">
-      <formula1>"Y,N,?"</formula1>
+      <formula1>YesNoMaybe</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick one" error="Choose Y (yes / met), N (no / not met), or ? (unknown)." sqref="C36:C37">
-      <formula1>"Y,N,?"</formula1>
+      <formula1>YesNoMaybe</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick one" error="Choose Y (yes / met), N (no / not met), or ? (unknown)." sqref="C39:C42">
-      <formula1>"Y,N,?"</formula1>
+      <formula1>YesNoMaybe</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
@@ -1895,7 +1958,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -1910,628 +1973,628 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="A1" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
+        <v>1</v>
+      </c>
+      <c r="B3" s="19">
+        <f>Inputs!B12</f>
+      </c>
+      <c r="C3" s="20">
+        <f>Inputs!C12</f>
+      </c>
+      <c r="D3" s="21">
+        <f>Inputs!D12</f>
+      </c>
+      <c r="E3" s="21">
+        <f>IF(D3="HIGH",3,IF(D3="MEDIUM",2,1))</f>
+      </c>
+      <c r="F3" s="21">
+        <f>IF(C3="Y",E3,IF(C3="?",E3/2,0))</f>
+      </c>
+      <c r="G3" s="21">
+        <f>IF(C3="Y","Pass",IF(C3="N",IF(D3="HIGH","Fail","Risk"),IF(C3="?","Open","—")))</f>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="13">
+        <v>2</v>
+      </c>
+      <c r="B4" s="22">
+        <f>Inputs!B13</f>
+      </c>
+      <c r="C4" s="23">
+        <f>Inputs!C13</f>
+      </c>
+      <c r="D4" s="24">
+        <f>Inputs!D13</f>
+      </c>
+      <c r="E4" s="24">
+        <f>IF(D4="HIGH",3,IF(D4="MEDIUM",2,1))</f>
+      </c>
+      <c r="F4" s="24">
+        <f>IF(C4="Y",E4,IF(C4="?",E4/2,0))</f>
+      </c>
+      <c r="G4" s="24">
+        <f>IF(C4="Y","Pass",IF(C4="N",IF(D4="HIGH","Fail","Risk"),IF(C4="?","Open","—")))</f>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>3</v>
+      </c>
+      <c r="B5" s="19">
+        <f>Inputs!B14</f>
+      </c>
+      <c r="C5" s="20">
+        <f>Inputs!C14</f>
+      </c>
+      <c r="D5" s="21">
+        <f>Inputs!D14</f>
+      </c>
+      <c r="E5" s="21">
+        <f>IF(D5="HIGH",3,IF(D5="MEDIUM",2,1))</f>
+      </c>
+      <c r="F5" s="21">
+        <f>IF(C5="Y",E5,IF(C5="?",E5/2,0))</f>
+      </c>
+      <c r="G5" s="21">
+        <f>IF(C5="Y","Pass",IF(C5="N",IF(D5="HIGH","Fail","Risk"),IF(C5="?","Open","—")))</f>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="13">
+        <v>4</v>
+      </c>
+      <c r="B6" s="22">
+        <f>Inputs!B15</f>
+      </c>
+      <c r="C6" s="23">
+        <f>Inputs!C15</f>
+      </c>
+      <c r="D6" s="24">
+        <f>Inputs!D15</f>
+      </c>
+      <c r="E6" s="24">
+        <f>IF(D6="HIGH",3,IF(D6="MEDIUM",2,1))</f>
+      </c>
+      <c r="F6" s="24">
+        <f>IF(C6="Y",E6,IF(C6="?",E6/2,0))</f>
+      </c>
+      <c r="G6" s="24">
+        <f>IF(C6="Y","Pass",IF(C6="N",IF(D6="HIGH","Fail","Risk"),IF(C6="?","Open","—")))</f>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>5</v>
+      </c>
+      <c r="B7" s="19">
+        <f>Inputs!B16</f>
+      </c>
+      <c r="C7" s="20">
+        <f>Inputs!C16</f>
+      </c>
+      <c r="D7" s="21">
+        <f>Inputs!D16</f>
+      </c>
+      <c r="E7" s="21">
+        <f>IF(D7="HIGH",3,IF(D7="MEDIUM",2,1))</f>
+      </c>
+      <c r="F7" s="21">
+        <f>IF(C7="Y",E7,IF(C7="?",E7/2,0))</f>
+      </c>
+      <c r="G7" s="21">
+        <f>IF(C7="Y","Pass",IF(C7="N",IF(D7="HIGH","Fail","Risk"),IF(C7="?","Open","—")))</f>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="13">
+        <v>6</v>
+      </c>
+      <c r="B8" s="22">
+        <f>Inputs!B18</f>
+      </c>
+      <c r="C8" s="23">
+        <f>Inputs!C18</f>
+      </c>
+      <c r="D8" s="24">
+        <f>Inputs!D18</f>
+      </c>
+      <c r="E8" s="24">
+        <f>IF(D8="HIGH",3,IF(D8="MEDIUM",2,1))</f>
+      </c>
+      <c r="F8" s="24">
+        <f>IF(C8="Y",E8,IF(C8="?",E8/2,0))</f>
+      </c>
+      <c r="G8" s="24">
+        <f>IF(C8="Y","Pass",IF(C8="N",IF(D8="HIGH","Fail","Risk"),IF(C8="?","Open","—")))</f>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="19">
+        <f>Inputs!B19</f>
+      </c>
+      <c r="C9" s="20">
+        <f>Inputs!C19</f>
+      </c>
+      <c r="D9" s="21">
+        <f>Inputs!D19</f>
+      </c>
+      <c r="E9" s="21">
+        <f>IF(D9="HIGH",3,IF(D9="MEDIUM",2,1))</f>
+      </c>
+      <c r="F9" s="21">
+        <f>IF(C9="Y",E9,IF(C9="?",E9/2,0))</f>
+      </c>
+      <c r="G9" s="21">
+        <f>IF(C9="Y","Pass",IF(C9="N",IF(D9="HIGH","Fail","Risk"),IF(C9="?","Open","—")))</f>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="13">
         <v>8</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>1</v>
-      </c>
-      <c r="B3" s="17">
-        <f>Inputs!B12</f>
-      </c>
-      <c r="C3" s="18">
-        <f>Inputs!C12</f>
-      </c>
-      <c r="D3" s="19">
-        <f>Inputs!D12</f>
-      </c>
-      <c r="E3" s="19">
-        <f>IF(D3="HIGH",3,IF(D3="MEDIUM",2,1))</f>
-      </c>
-      <c r="F3" s="19">
-        <f>IF(C3="Y",E3,IF(C3="?",E3/2,0))</f>
-      </c>
-      <c r="G3" s="19">
-        <f>IF(C3="Y","Pass",IF(C3="N",IF(D3="HIGH","Fail","Risk"),IF(C3="?","Open","—")))</f>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
-        <v>2</v>
-      </c>
-      <c r="B4" s="20">
-        <f>Inputs!B13</f>
-      </c>
-      <c r="C4" s="21">
-        <f>Inputs!C13</f>
-      </c>
-      <c r="D4" s="22">
-        <f>Inputs!D13</f>
-      </c>
-      <c r="E4" s="22">
-        <f>IF(D4="HIGH",3,IF(D4="MEDIUM",2,1))</f>
-      </c>
-      <c r="F4" s="22">
-        <f>IF(C4="Y",E4,IF(C4="?",E4/2,0))</f>
-      </c>
-      <c r="G4" s="22">
-        <f>IF(C4="Y","Pass",IF(C4="N",IF(D4="HIGH","Fail","Risk"),IF(C4="?","Open","—")))</f>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>3</v>
-      </c>
-      <c r="B5" s="17">
-        <f>Inputs!B14</f>
-      </c>
-      <c r="C5" s="18">
-        <f>Inputs!C14</f>
-      </c>
-      <c r="D5" s="19">
-        <f>Inputs!D14</f>
-      </c>
-      <c r="E5" s="19">
-        <f>IF(D5="HIGH",3,IF(D5="MEDIUM",2,1))</f>
-      </c>
-      <c r="F5" s="19">
-        <f>IF(C5="Y",E5,IF(C5="?",E5/2,0))</f>
-      </c>
-      <c r="G5" s="19">
-        <f>IF(C5="Y","Pass",IF(C5="N",IF(D5="HIGH","Fail","Risk"),IF(C5="?","Open","—")))</f>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
-        <v>4</v>
-      </c>
-      <c r="B6" s="20">
-        <f>Inputs!B15</f>
-      </c>
-      <c r="C6" s="21">
-        <f>Inputs!C15</f>
-      </c>
-      <c r="D6" s="22">
-        <f>Inputs!D15</f>
-      </c>
-      <c r="E6" s="22">
-        <f>IF(D6="HIGH",3,IF(D6="MEDIUM",2,1))</f>
-      </c>
-      <c r="F6" s="22">
-        <f>IF(C6="Y",E6,IF(C6="?",E6/2,0))</f>
-      </c>
-      <c r="G6" s="22">
-        <f>IF(C6="Y","Pass",IF(C6="N",IF(D6="HIGH","Fail","Risk"),IF(C6="?","Open","—")))</f>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="17">
-        <f>Inputs!B16</f>
-      </c>
-      <c r="C7" s="18">
-        <f>Inputs!C16</f>
-      </c>
-      <c r="D7" s="19">
-        <f>Inputs!D16</f>
-      </c>
-      <c r="E7" s="19">
-        <f>IF(D7="HIGH",3,IF(D7="MEDIUM",2,1))</f>
-      </c>
-      <c r="F7" s="19">
-        <f>IF(C7="Y",E7,IF(C7="?",E7/2,0))</f>
-      </c>
-      <c r="G7" s="19">
-        <f>IF(C7="Y","Pass",IF(C7="N",IF(D7="HIGH","Fail","Risk"),IF(C7="?","Open","—")))</f>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
-        <v>6</v>
-      </c>
-      <c r="B8" s="20">
-        <f>Inputs!B18</f>
-      </c>
-      <c r="C8" s="21">
-        <f>Inputs!C18</f>
-      </c>
-      <c r="D8" s="22">
-        <f>Inputs!D18</f>
-      </c>
-      <c r="E8" s="22">
-        <f>IF(D8="HIGH",3,IF(D8="MEDIUM",2,1))</f>
-      </c>
-      <c r="F8" s="22">
-        <f>IF(C8="Y",E8,IF(C8="?",E8/2,0))</f>
-      </c>
-      <c r="G8" s="22">
-        <f>IF(C8="Y","Pass",IF(C8="N",IF(D8="HIGH","Fail","Risk"),IF(C8="?","Open","—")))</f>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>7</v>
-      </c>
-      <c r="B9" s="17">
-        <f>Inputs!B19</f>
-      </c>
-      <c r="C9" s="18">
-        <f>Inputs!C19</f>
-      </c>
-      <c r="D9" s="19">
-        <f>Inputs!D19</f>
-      </c>
-      <c r="E9" s="19">
-        <f>IF(D9="HIGH",3,IF(D9="MEDIUM",2,1))</f>
-      </c>
-      <c r="F9" s="19">
-        <f>IF(C9="Y",E9,IF(C9="?",E9/2,0))</f>
-      </c>
-      <c r="G9" s="19">
-        <f>IF(C9="Y","Pass",IF(C9="N",IF(D9="HIGH","Fail","Risk"),IF(C9="?","Open","—")))</f>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
-        <v>8</v>
-      </c>
-      <c r="B10" s="20">
+      <c r="B10" s="22">
         <f>Inputs!B20</f>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="23">
         <f>Inputs!C20</f>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="24">
         <f>Inputs!D20</f>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="24">
         <f>IF(D10="HIGH",3,IF(D10="MEDIUM",2,1))</f>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="24">
         <f>IF(C10="Y",E10,IF(C10="?",E10/2,0))</f>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="24">
         <f>IF(C10="Y","Pass",IF(C10="N",IF(D10="HIGH","Fail","Risk"),IF(C10="?","Open","—")))</f>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="9">
         <v>9</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="19">
         <f>Inputs!B22</f>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="20">
         <f>Inputs!C22</f>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="21">
         <f>Inputs!D22</f>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="21">
         <f>IF(D11="HIGH",3,IF(D11="MEDIUM",2,1))</f>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="21">
         <f>IF(C11="Y",E11,IF(C11="?",E11/2,0))</f>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="21">
         <f>IF(C11="Y","Pass",IF(C11="N",IF(D11="HIGH","Fail","Risk"),IF(C11="?","Open","—")))</f>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
+      <c r="A12" s="13">
         <v>10</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="22">
         <f>Inputs!B23</f>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="23">
         <f>Inputs!C23</f>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="24">
         <f>Inputs!D23</f>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="24">
         <f>IF(D12="HIGH",3,IF(D12="MEDIUM",2,1))</f>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="24">
         <f>IF(C12="Y",E12,IF(C12="?",E12/2,0))</f>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="24">
         <f>IF(C12="Y","Pass",IF(C12="N",IF(D12="HIGH","Fail","Risk"),IF(C12="?","Open","—")))</f>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="9">
         <v>11</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="19">
         <f>Inputs!B24</f>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="20">
         <f>Inputs!C24</f>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="21">
         <f>Inputs!D24</f>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="21">
         <f>IF(D13="HIGH",3,IF(D13="MEDIUM",2,1))</f>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="21">
         <f>IF(C13="Y",E13,IF(C13="?",E13/2,0))</f>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="21">
         <f>IF(C13="Y","Pass",IF(C13="N",IF(D13="HIGH","Fail","Risk"),IF(C13="?","Open","—")))</f>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
+      <c r="A14" s="13">
         <v>12</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="22">
         <f>Inputs!B26</f>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="23">
         <f>Inputs!C26</f>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="24">
         <f>Inputs!D26</f>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="24">
         <f>IF(D14="HIGH",3,IF(D14="MEDIUM",2,1))</f>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="24">
         <f>IF(C14="Y",E14,IF(C14="?",E14/2,0))</f>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="24">
         <f>IF(C14="Y","Pass",IF(C14="N",IF(D14="HIGH","Fail","Risk"),IF(C14="?","Open","—")))</f>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="A15" s="9">
         <v>13</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="19">
         <f>Inputs!B27</f>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="20">
         <f>Inputs!C27</f>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="21">
         <f>Inputs!D27</f>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="21">
         <f>IF(D15="HIGH",3,IF(D15="MEDIUM",2,1))</f>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="21">
         <f>IF(C15="Y",E15,IF(C15="?",E15/2,0))</f>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="21">
         <f>IF(C15="Y","Pass",IF(C15="N",IF(D15="HIGH","Fail","Risk"),IF(C15="?","Open","—")))</f>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="11">
+      <c r="A16" s="13">
         <v>14</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="22">
         <f>Inputs!B28</f>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="23">
         <f>Inputs!C28</f>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="24">
         <f>Inputs!D28</f>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="24">
         <f>IF(D16="HIGH",3,IF(D16="MEDIUM",2,1))</f>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="24">
         <f>IF(C16="Y",E16,IF(C16="?",E16/2,0))</f>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="24">
         <f>IF(C16="Y","Pass",IF(C16="N",IF(D16="HIGH","Fail","Risk"),IF(C16="?","Open","—")))</f>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17" s="9">
         <v>15</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="19">
         <f>Inputs!B29</f>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="20">
         <f>Inputs!C29</f>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="21">
         <f>Inputs!D29</f>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="21">
         <f>IF(D17="HIGH",3,IF(D17="MEDIUM",2,1))</f>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="21">
         <f>IF(C17="Y",E17,IF(C17="?",E17/2,0))</f>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="21">
         <f>IF(C17="Y","Pass",IF(C17="N",IF(D17="HIGH","Fail","Risk"),IF(C17="?","Open","—")))</f>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="11">
+      <c r="A18" s="13">
         <v>16</v>
       </c>
-      <c r="B18" s="20">
+      <c r="B18" s="22">
         <f>Inputs!B31</f>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="23">
         <f>Inputs!C31</f>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="24">
         <f>Inputs!D31</f>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="24">
         <f>IF(D18="HIGH",3,IF(D18="MEDIUM",2,1))</f>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="24">
         <f>IF(C18="Y",E18,IF(C18="?",E18/2,0))</f>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="24">
         <f>IF(C18="Y","Pass",IF(C18="N",IF(D18="HIGH","Fail","Risk"),IF(C18="?","Open","—")))</f>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
+      <c r="A19" s="9">
         <v>17</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="19">
         <f>Inputs!B32</f>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="20">
         <f>Inputs!C32</f>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="21">
         <f>Inputs!D32</f>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="21">
         <f>IF(D19="HIGH",3,IF(D19="MEDIUM",2,1))</f>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="21">
         <f>IF(C19="Y",E19,IF(C19="?",E19/2,0))</f>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="21">
         <f>IF(C19="Y","Pass",IF(C19="N",IF(D19="HIGH","Fail","Risk"),IF(C19="?","Open","—")))</f>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="11">
+      <c r="A20" s="13">
         <v>18</v>
       </c>
-      <c r="B20" s="20">
+      <c r="B20" s="22">
         <f>Inputs!B33</f>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="23">
         <f>Inputs!C33</f>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="24">
         <f>Inputs!D33</f>
       </c>
-      <c r="E20" s="22">
+      <c r="E20" s="24">
         <f>IF(D20="HIGH",3,IF(D20="MEDIUM",2,1))</f>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="24">
         <f>IF(C20="Y",E20,IF(C20="?",E20/2,0))</f>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="24">
         <f>IF(C20="Y","Pass",IF(C20="N",IF(D20="HIGH","Fail","Risk"),IF(C20="?","Open","—")))</f>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
+      <c r="A21" s="9">
         <v>19</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="19">
         <f>Inputs!B34</f>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="20">
         <f>Inputs!C34</f>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="21">
         <f>Inputs!D34</f>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="21">
         <f>IF(D21="HIGH",3,IF(D21="MEDIUM",2,1))</f>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="21">
         <f>IF(C21="Y",E21,IF(C21="?",E21/2,0))</f>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="21">
         <f>IF(C21="Y","Pass",IF(C21="N",IF(D21="HIGH","Fail","Risk"),IF(C21="?","Open","—")))</f>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="11">
+      <c r="A22" s="13">
         <v>20</v>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="22">
         <f>Inputs!B36</f>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="23">
         <f>Inputs!C36</f>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="24">
         <f>Inputs!D36</f>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="24">
         <f>IF(D22="HIGH",3,IF(D22="MEDIUM",2,1))</f>
       </c>
-      <c r="F22" s="22">
+      <c r="F22" s="24">
         <f>IF(C22="Y",E22,IF(C22="?",E22/2,0))</f>
       </c>
-      <c r="G22" s="22">
+      <c r="G22" s="24">
         <f>IF(C22="Y","Pass",IF(C22="N",IF(D22="HIGH","Fail","Risk"),IF(C22="?","Open","—")))</f>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
+      <c r="A23" s="9">
         <v>21</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="19">
         <f>Inputs!B37</f>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="20">
         <f>Inputs!C37</f>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="21">
         <f>Inputs!D37</f>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="21">
         <f>IF(D23="HIGH",3,IF(D23="MEDIUM",2,1))</f>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="21">
         <f>IF(C23="Y",E23,IF(C23="?",E23/2,0))</f>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="21">
         <f>IF(C23="Y","Pass",IF(C23="N",IF(D23="HIGH","Fail","Risk"),IF(C23="?","Open","—")))</f>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="11">
+      <c r="A24" s="13">
         <v>22</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="22">
         <f>Inputs!B39</f>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="23">
         <f>Inputs!C39</f>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="24">
         <f>Inputs!D39</f>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="24">
         <f>IF(D24="HIGH",3,IF(D24="MEDIUM",2,1))</f>
       </c>
-      <c r="F24" s="22">
+      <c r="F24" s="24">
         <f>IF(C24="Y",E24,IF(C24="?",E24/2,0))</f>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="24">
         <f>IF(C24="Y","Pass",IF(C24="N",IF(D24="HIGH","Fail","Risk"),IF(C24="?","Open","—")))</f>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
+      <c r="A25" s="9">
         <v>23</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="19">
         <f>Inputs!B40</f>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="20">
         <f>Inputs!C40</f>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="21">
         <f>Inputs!D40</f>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="21">
         <f>IF(D25="HIGH",3,IF(D25="MEDIUM",2,1))</f>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="21">
         <f>IF(C25="Y",E25,IF(C25="?",E25/2,0))</f>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="21">
         <f>IF(C25="Y","Pass",IF(C25="N",IF(D25="HIGH","Fail","Risk"),IF(C25="?","Open","—")))</f>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="11">
+      <c r="A26" s="13">
         <v>24</v>
       </c>
-      <c r="B26" s="20">
+      <c r="B26" s="22">
         <f>Inputs!B41</f>
       </c>
-      <c r="C26" s="21">
+      <c r="C26" s="23">
         <f>Inputs!C41</f>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="24">
         <f>Inputs!D41</f>
       </c>
-      <c r="E26" s="22">
+      <c r="E26" s="24">
         <f>IF(D26="HIGH",3,IF(D26="MEDIUM",2,1))</f>
       </c>
-      <c r="F26" s="22">
+      <c r="F26" s="24">
         <f>IF(C26="Y",E26,IF(C26="?",E26/2,0))</f>
       </c>
-      <c r="G26" s="22">
+      <c r="G26" s="24">
         <f>IF(C26="Y","Pass",IF(C26="N",IF(D26="HIGH","Fail","Risk"),IF(C26="?","Open","—")))</f>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
+      <c r="A27" s="9">
         <v>25</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="19">
         <f>Inputs!B42</f>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="20">
         <f>Inputs!C42</f>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="21">
         <f>Inputs!D42</f>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="21">
         <f>IF(D27="HIGH",3,IF(D27="MEDIUM",2,1))</f>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="21">
         <f>IF(C27="Y",E27,IF(C27="?",E27/2,0))</f>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="21">
         <f>IF(C27="Y","Pass",IF(C27="N",IF(D27="HIGH","Fail","Risk"),IF(C27="?","Open","—")))</f>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="24">
+      <c r="A29" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="26">
         <f>SUM(E3:E27)</f>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="26">
         <f>SUM(F3:F27)</f>
       </c>
-      <c r="G29" s="25">
+      <c r="G29" s="27">
         <f>IF(E29=0,0,F29/E29)</f>
       </c>
     </row>
@@ -2549,7 +2612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2564,212 +2627,212 @@
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" ht="22" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="27">
+      <c r="B3" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="28"/>
+      <c r="D3" s="29">
         <f>IF(BusinessName="","(not set)",BusinessName)</f>
       </c>
-      <c r="E3" s="27"/>
+      <c r="E3" s="29"/>
     </row>
     <row r="4" ht="22" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="28">
+      <c r="B4" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="28"/>
+      <c r="D4" s="30">
         <f>IF(OwnerNames="","(not set)",OwnerNames)</f>
       </c>
-      <c r="E4" s="28"/>
+      <c r="E4" s="30"/>
     </row>
     <row r="5" ht="22" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="28">
+      <c r="B5" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="30">
         <f>IF(EvalDate="","(not set)",EvalDate)</f>
       </c>
-      <c r="E5" s="28"/>
+      <c r="E5" s="30"/>
     </row>
     <row r="7" ht="22" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
+      <c r="B7" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="9">
+      <c r="B8" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="11">
         <f>COUNTIF(MetResponses,"Y")</f>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="32">
+      <c r="B9" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="34">
         <f>COUNTIF(MetResponses,"N")</f>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="9">
+      <c r="B10" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="11">
         <f>COUNTIF(MetResponses,"?")</f>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="32">
+      <c r="B11" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="34">
         <f>COUNTBLANK(MetResponses)</f>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="9">
+      <c r="B12" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="11">
         <f>SUMPRODUCT((MetResponses="N")*(RiskLevels="HIGH"))</f>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32">
+      <c r="B13" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="34">
         <f>SUMPRODUCT((MetResponses="N")*(RiskLevels="MEDIUM"))</f>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="9">
+      <c r="B14" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="11">
         <f>COUNTA(RiskLevels)</f>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
+      <c r="B16" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
     </row>
     <row r="17" ht="40" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="34">
+      <c r="B17" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="36">
         <f>ReadinessPct</f>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
+      <c r="B19" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
     </row>
     <row r="20" ht="58" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="35">
+      <c r="B20" s="37">
         <f>IF(SUMPRODUCT((MetResponses="N")*(RiskLevels="HIGH"))&gt;0,"INELIGIBLE: one or more high-risk requirements failed. Fix the N + HIGH items on the Inputs tab before applying.",IF(COUNTBLANK(MetResponses)+COUNTIF(MetResponses,"?")&gt;5,"INCOMPLETE: too many open or unanswered items. Resolve the ? entries first.",IF(ReadinessPct&gt;=0.85,"LIKELY ELIGIBLE: schedule a free pre-application meeting with your SBA District Office and a GovCon attorney before submitting through certify.sba.gov.",IF(ReadinessPct&gt;=0.6,"POSSIBLE: you have most pieces in place. Close the N and ? items on the Inputs tab before you start the formal application.","NOT READY: significant gaps. Focus first on small-business status, owner control, and the $850K net worth test."))))</f>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
     </row>
     <row r="22" ht="22" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
+      <c r="B22" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
     </row>
     <row r="23" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" s="37">
+      <c r="B23" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="39">
         <f>IF(SUMPRODUCT((MetResponses="N")*(RiskLevels="HIGH"))&gt;0,"Fix every N + HIGH row on the Inputs tab. Most common: net worth above $850K, owner does not control daily operations, or business is not yet 2 years old.","No high-risk gaps. Good.")</f>
       </c>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
     </row>
     <row r="24" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="39">
+      <c r="B24" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="41">
         <f>"3 years of business + personal tax returns; current personal financial statement; operating agreement / bylaws; org chart with titles; SAM.gov registration confirmation; bank statements in firm name."</f>
       </c>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
     </row>
     <row r="25" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B25" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" s="37">
+      <c r="B25" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="39">
         <f>"Create MySBA account at certify.sba.gov. Application review target is 90 days. If declined, request reconsideration within 45 days or appeal to OHA."</f>
       </c>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
     </row>
     <row r="26" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B26" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="39">
+      <c r="B26" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="41">
         <f>"Book a pre-application meeting with your SBA District Office Business Opportunity Specialist (BOS). It is free and they will pre-screen your application before you submit."</f>
       </c>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
     </row>
     <row r="28" ht="50" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B28" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
+      <c r="B28" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -2837,7 +2900,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2851,119 +2914,119 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" s="29"/>
+      <c r="B3" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="31"/>
     </row>
     <row r="4" ht="40" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="37"/>
+      <c r="B4" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="39"/>
     </row>
     <row r="6" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" s="29"/>
+      <c r="B6" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="31"/>
     </row>
     <row r="7" ht="80" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" s="37"/>
+      <c r="B7" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="39"/>
     </row>
     <row r="9" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="29"/>
+      <c r="B9" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="31"/>
     </row>
     <row r="10" ht="40" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="37"/>
+      <c r="B10" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="39"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="29"/>
+      <c r="B12" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="31"/>
     </row>
     <row r="13" ht="112" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="37"/>
+      <c r="B13" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="39"/>
     </row>
     <row r="15" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" s="29"/>
+      <c r="B15" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="31"/>
     </row>
     <row r="16" ht="96" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="37"/>
+      <c r="B16" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="39"/>
     </row>
     <row r="18" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" s="29"/>
+      <c r="B18" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="31"/>
     </row>
     <row r="19" ht="96" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" s="37"/>
+      <c r="B19" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="39"/>
     </row>
     <row r="21" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="29"/>
+      <c r="B21" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="31"/>
     </row>
     <row r="22" ht="80" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="37"/>
+      <c r="B22" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="39"/>
     </row>
     <row r="24" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" s="29"/>
+      <c r="B24" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="31"/>
     </row>
     <row r="25" ht="40" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" s="37"/>
+      <c r="B25" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="39"/>
     </row>
     <row r="27" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="C27" s="29"/>
+      <c r="B27" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" s="31"/>
     </row>
     <row r="28" ht="40" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" s="37"/>
+      <c r="B28" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -2996,7 +3059,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3010,95 +3073,95 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="29" t="s">
-        <v>97</v>
-      </c>
-      <c r="C3" s="29"/>
+      <c r="B3" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="31"/>
     </row>
     <row r="4" ht="40" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="37"/>
+      <c r="B4" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="39"/>
     </row>
     <row r="6" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="29" t="s">
-        <v>99</v>
-      </c>
-      <c r="C6" s="29"/>
+      <c r="B6" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="31"/>
     </row>
     <row r="7" ht="96" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="37"/>
+      <c r="B7" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="39"/>
     </row>
     <row r="9" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="29"/>
+      <c r="B9" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="31"/>
     </row>
     <row r="10" ht="112" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="C10" s="37"/>
+      <c r="B10" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="39"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="29"/>
+      <c r="B12" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="31"/>
     </row>
     <row r="13" ht="112" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="37"/>
+      <c r="B13" s="39" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="39"/>
     </row>
     <row r="15" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="29"/>
+      <c r="B15" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="31"/>
     </row>
     <row r="16" ht="96" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="37"/>
+      <c r="B16" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="39"/>
     </row>
     <row r="18" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" s="29"/>
+      <c r="B18" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" s="31"/>
     </row>
     <row r="19" ht="96" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="C19" s="37"/>
+      <c r="B19" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="39"/>
     </row>
     <row r="21" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" s="29"/>
+      <c r="B21" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" s="31"/>
     </row>
     <row r="22" ht="80" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="C22" s="37"/>
+      <c r="B22" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="15">
